--- a/output/exports/test_verification_export.xlsx
+++ b/output/exports/test_verification_export.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>AI HAZOP Study Agent (Gemini 3.7 Flash &amp; Google ADK)</t>
+          <t>AI HAZOP Study Agent (Gemini 3.8 Flash &amp; Google ADK)</t>
         </is>
       </c>
     </row>
